--- a/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle.xlsx
+++ b/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5238" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5212" uniqueCount="387">
   <si>
     <t>Property</t>
   </si>
@@ -271,8 +271,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
-bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
+    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -387,16 +387,6 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -499,9 +489,6 @@
 This specification defines some specific uses of Bundle.link for [searching](http://hl7.org/fhir/R4/search.html#conformance) and [paging](http://hl7.org/fhir/R4/http.html#paging), but no specific uses for Bundle.entry.link, and no defined function in a transaction - the meaning is implementation specific.</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.link.id</t>
   </si>
   <si>
@@ -518,6 +505,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -538,16 +528,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -584,9 +564,6 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -594,9 +571,6 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -618,8 +592,8 @@
     <t>closed</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
+    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -668,9 +642,6 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -680,8 +651,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-2</t>
+    <t xml:space="preserve">bdl-2
+</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -737,8 +708,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-3</t>
+    <t xml:space="preserve">bdl-3
+</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -792,9 +763,6 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -822,8 +790,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-4</t>
+    <t xml:space="preserve">bdl-4
+</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1606,15 +1574,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="57.64453125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -2403,30 +2371,30 @@
         <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2452,13 +2420,13 @@
         <v>108</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2466,32 +2434,32 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="Z8" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>133</v>
-      </c>
       <c r="AA8" t="s" s="2">
         <v>78</v>
       </c>
@@ -2508,7 +2476,7 @@
         <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>88</v>
@@ -2532,15 +2500,15 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2563,16 +2531,16 @@
         <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2622,7 +2590,7 @@
         <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2643,18 +2611,18 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2677,16 +2645,16 @@
         <v>89</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2736,7 +2704,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2745,7 +2713,7 @@
         <v>88</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>100</v>
@@ -2765,10 +2733,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2791,16 +2759,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2850,7 +2818,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2859,7 +2827,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>100</v>
@@ -2868,7 +2836,7 @@
         <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>78</v>
@@ -2879,10 +2847,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2905,13 +2873,13 @@
         <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2962,7 +2930,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2980,7 +2948,7 @@
         <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
@@ -2991,14 +2959,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3017,16 +2985,16 @@
         <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3064,19 +3032,19 @@
         <v>78</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3088,13 +3056,13 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -3105,14 +3073,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3131,19 +3099,19 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O14" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3192,7 +3160,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3204,7 +3172,7 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -3221,10 +3189,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3247,17 +3215,15 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3306,7 +3272,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -3335,10 +3301,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3364,14 +3330,12 @@
         <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -3420,7 +3384,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3449,10 +3413,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3460,7 +3424,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>80</v>
@@ -3475,13 +3439,13 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3520,17 +3484,17 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3539,16 +3503,16 @@
         <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3559,10 +3523,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3585,13 +3549,13 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3642,7 +3606,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3660,7 +3624,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3671,14 +3635,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3697,16 +3661,16 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3744,19 +3708,19 @@
         <v>78</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3768,13 +3732,13 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -3785,14 +3749,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3811,19 +3775,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O20" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3872,7 +3836,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3884,7 +3848,7 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -3901,10 +3865,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3930,10 +3894,10 @@
         <v>78</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3984,7 +3948,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3996,7 +3960,7 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
@@ -4013,10 +3977,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4042,13 +4006,13 @@
         <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4098,7 +4062,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4127,10 +4091,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4153,13 +4117,13 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4210,7 +4174,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4228,7 +4192,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4239,10 +4203,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4265,13 +4229,13 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4322,7 +4286,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4331,7 +4295,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
@@ -4340,7 +4304,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4351,10 +4315,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4377,13 +4341,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4434,7 +4398,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4452,7 +4416,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4463,14 +4427,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4489,16 +4453,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4536,19 +4500,19 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4560,13 +4524,13 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4577,14 +4541,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4603,19 +4567,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O27" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4664,7 +4628,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4676,7 +4640,7 @@
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4693,10 +4657,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4722,13 +4686,13 @@
         <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4754,13 +4718,13 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -4778,7 +4742,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4807,10 +4771,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4833,16 +4797,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4892,7 +4856,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4921,10 +4885,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4947,13 +4911,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5004,7 +4968,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5013,7 +4977,7 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>100</v>
@@ -5022,7 +4986,7 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5033,10 +4997,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5059,13 +5023,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5116,7 +5080,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5134,7 +5098,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5145,14 +5109,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5171,16 +5135,16 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5218,19 +5182,19 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5242,13 +5206,13 @@
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5259,14 +5223,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5285,19 +5249,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O33" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5346,7 +5310,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5358,7 +5322,7 @@
         <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -5375,10 +5339,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5404,10 +5368,10 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5434,13 +5398,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5458,7 +5422,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>88</v>
@@ -5487,10 +5451,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5516,13 +5480,13 @@
         <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5572,7 +5536,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>88</v>
@@ -5601,10 +5565,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5627,17 +5591,15 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5686,7 +5648,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5715,10 +5677,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5741,17 +5703,15 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5800,7 +5760,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5829,10 +5789,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5855,17 +5815,15 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5914,7 +5872,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5943,10 +5901,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5969,17 +5927,15 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6028,7 +5984,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6057,10 +6013,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6083,13 +6039,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6140,7 +6096,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6149,7 +6105,7 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -6158,7 +6114,7 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6169,10 +6125,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6195,13 +6151,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6252,7 +6208,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6270,7 +6226,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6281,14 +6237,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6307,16 +6263,16 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6354,19 +6310,19 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6378,13 +6334,13 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6395,14 +6351,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6421,19 +6377,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O43" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6482,7 +6438,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6494,7 +6450,7 @@
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -6511,10 +6467,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6537,17 +6493,15 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6596,7 +6550,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6625,10 +6579,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6654,14 +6608,12 @@
         <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6710,7 +6662,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6739,10 +6691,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6765,16 +6717,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6824,7 +6776,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6853,10 +6805,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6879,16 +6831,16 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6938,7 +6890,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6967,10 +6919,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6993,16 +6945,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7052,7 +7004,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7070,7 +7022,7 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7081,13 +7033,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>78</v>
@@ -7109,13 +7061,13 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7166,7 +7118,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7175,16 +7127,16 @@
         <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7195,10 +7147,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7221,13 +7173,13 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7278,7 +7230,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7296,7 +7248,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7307,14 +7259,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7333,16 +7285,16 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7380,19 +7332,19 @@
         <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7404,13 +7356,13 @@
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7421,14 +7373,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7447,19 +7399,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O52" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7508,7 +7460,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7520,7 +7472,7 @@
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
@@ -7537,10 +7489,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7566,10 +7518,10 @@
         <v>78</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7620,7 +7572,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7632,7 +7584,7 @@
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -7649,10 +7601,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7678,13 +7630,13 @@
         <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7734,7 +7686,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7763,10 +7715,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7789,16 +7741,16 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7848,7 +7800,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7866,10 +7818,10 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -7877,10 +7829,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7903,13 +7855,13 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7960,7 +7912,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -7969,7 +7921,7 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
@@ -7978,7 +7930,7 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -7989,10 +7941,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8015,13 +7967,13 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8072,7 +8024,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8090,7 +8042,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8101,14 +8053,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8127,16 +8079,16 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8174,19 +8126,19 @@
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8198,13 +8150,13 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8215,14 +8167,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8241,19 +8193,19 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8302,7 +8254,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8314,7 +8266,7 @@
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -8331,10 +8283,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8360,13 +8312,13 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8392,13 +8344,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8416,7 +8368,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8445,10 +8397,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8471,16 +8423,16 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8530,7 +8482,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8559,10 +8511,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8585,13 +8537,13 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8642,7 +8594,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8651,7 +8603,7 @@
         <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>100</v>
@@ -8660,7 +8612,7 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -8671,10 +8623,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8697,13 +8649,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8754,7 +8706,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8772,7 +8724,7 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -8783,14 +8735,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8809,16 +8761,16 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8856,19 +8808,19 @@
         <v>78</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -8880,13 +8832,13 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -8897,14 +8849,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8923,19 +8875,19 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O65" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -8984,7 +8936,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -8996,7 +8948,7 @@
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -9013,10 +8965,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9042,10 +8994,10 @@
         <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9072,13 +9024,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9096,7 +9048,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>88</v>
@@ -9125,10 +9077,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9154,13 +9106,13 @@
         <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9210,7 +9162,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>88</v>
@@ -9239,10 +9191,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9265,17 +9217,15 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9324,7 +9274,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9353,10 +9303,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9379,17 +9329,15 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -9438,7 +9386,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9467,10 +9415,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9493,17 +9441,15 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -9552,7 +9498,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9581,10 +9527,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9607,17 +9553,15 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -9666,7 +9610,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9695,10 +9639,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9721,13 +9665,13 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9778,7 +9722,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -9787,7 +9731,7 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>100</v>
@@ -9796,7 +9740,7 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -9807,10 +9751,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9833,13 +9777,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9890,7 +9834,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -9908,7 +9852,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -9919,14 +9863,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9945,16 +9889,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9992,19 +9936,19 @@
         <v>78</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10016,13 +9960,13 @@
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10033,14 +9977,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10059,19 +10003,19 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10120,7 +10064,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10132,7 +10076,7 @@
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -10149,10 +10093,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10175,17 +10119,15 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10234,7 +10176,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>88</v>
@@ -10263,10 +10205,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10292,14 +10234,12 @@
         <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10348,7 +10288,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10377,10 +10317,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10403,16 +10343,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10462,7 +10402,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10491,10 +10431,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10517,16 +10457,16 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10576,7 +10516,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10605,10 +10545,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10631,16 +10571,16 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10690,7 +10630,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -10708,7 +10648,7 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -10719,13 +10659,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>78</v>
@@ -10747,13 +10687,13 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10804,7 +10744,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -10813,16 +10753,16 @@
         <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -10833,10 +10773,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10859,13 +10799,13 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10916,7 +10856,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -10934,7 +10874,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -10945,14 +10885,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10971,16 +10911,16 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11018,19 +10958,19 @@
         <v>78</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11042,13 +10982,13 @@
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11059,14 +10999,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11085,19 +11025,19 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L84" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -11146,7 +11086,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11158,7 +11098,7 @@
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -11175,10 +11115,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11204,10 +11144,10 @@
         <v>78</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11258,7 +11198,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11270,7 +11210,7 @@
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -11287,10 +11227,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11316,13 +11256,13 @@
         <v>102</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11372,7 +11312,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11401,10 +11341,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11427,13 +11367,13 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11484,7 +11424,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -11502,7 +11442,7 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -11513,10 +11453,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11539,13 +11479,13 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11596,7 +11536,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -11605,7 +11545,7 @@
         <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>100</v>
@@ -11614,7 +11554,7 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -11625,10 +11565,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11651,13 +11591,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11708,7 +11648,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -11726,7 +11666,7 @@
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -11737,14 +11677,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11763,16 +11703,16 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11810,19 +11750,19 @@
         <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -11834,13 +11774,13 @@
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -11851,14 +11791,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11877,19 +11817,19 @@
         <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L91" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O91" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -11938,7 +11878,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -11950,7 +11890,7 @@
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -11967,10 +11907,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11996,13 +11936,13 @@
         <v>108</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12028,13 +11968,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -12052,7 +11992,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12081,10 +12021,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12107,16 +12047,16 @@
         <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12166,7 +12106,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12195,10 +12135,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12221,13 +12161,13 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12278,7 +12218,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12287,7 +12227,7 @@
         <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>100</v>
@@ -12296,7 +12236,7 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -12307,10 +12247,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12333,13 +12273,13 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12390,7 +12330,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -12408,7 +12348,7 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -12419,14 +12359,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12445,16 +12385,16 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12492,19 +12432,19 @@
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -12516,13 +12456,13 @@
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -12533,14 +12473,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12559,19 +12499,19 @@
         <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L97" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -12620,7 +12560,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -12632,7 +12572,7 @@
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
@@ -12649,10 +12589,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12678,10 +12618,10 @@
         <v>108</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12708,13 +12648,13 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -12732,7 +12672,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>88</v>
@@ -12761,10 +12701,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12790,13 +12730,13 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12846,7 +12786,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>88</v>
@@ -12875,10 +12815,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12901,17 +12841,15 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -12960,7 +12898,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -12989,10 +12927,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13015,17 +12953,15 @@
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -13074,7 +13010,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13103,10 +13039,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13129,17 +13065,15 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -13188,7 +13122,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13217,10 +13151,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13243,17 +13177,15 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -13302,7 +13234,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -13331,10 +13263,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13357,13 +13289,13 @@
         <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13414,7 +13346,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -13423,7 +13355,7 @@
         <v>88</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>100</v>
@@ -13432,7 +13364,7 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -13443,10 +13375,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13469,13 +13401,13 @@
         <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13526,7 +13458,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -13544,7 +13476,7 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -13555,14 +13487,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13581,16 +13513,16 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N106" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13628,19 +13560,19 @@
         <v>78</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -13652,13 +13584,13 @@
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -13669,14 +13601,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13695,19 +13627,19 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L107" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O107" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -13756,7 +13688,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -13768,7 +13700,7 @@
         <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>78</v>
@@ -13785,10 +13717,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13811,17 +13743,15 @@
         <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -13870,7 +13800,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>88</v>
@@ -13899,10 +13829,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13928,14 +13858,12 @@
         <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -13984,7 +13912,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14013,10 +13941,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14039,16 +13967,16 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14098,7 +14026,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14127,10 +14055,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14153,16 +14081,16 @@
         <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14212,7 +14140,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14241,10 +14169,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14267,16 +14195,16 @@
         <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14326,7 +14254,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -14344,7 +14272,7 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -14355,13 +14283,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>78</v>
@@ -14383,13 +14311,13 @@
         <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14440,7 +14368,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -14449,16 +14377,16 @@
         <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -14469,10 +14397,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14495,13 +14423,13 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14552,7 +14480,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -14570,7 +14498,7 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>
@@ -14581,14 +14509,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -14607,16 +14535,16 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N115" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14654,19 +14582,19 @@
         <v>78</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -14678,13 +14606,13 @@
         <v>78</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>
@@ -14695,14 +14623,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -14721,19 +14649,19 @@
         <v>89</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L116" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O116" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -14782,7 +14710,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -14794,7 +14722,7 @@
         <v>78</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>78</v>
@@ -14811,10 +14739,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14840,10 +14768,10 @@
         <v>78</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14894,7 +14822,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -14906,7 +14834,7 @@
         <v>78</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>78</v>
@@ -14923,10 +14851,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14952,13 +14880,13 @@
         <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15008,7 +14936,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -15037,10 +14965,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15063,16 +14991,16 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15122,7 +15050,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -15140,7 +15068,7 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>78</v>
@@ -15151,10 +15079,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15177,13 +15105,13 @@
         <v>89</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15234,7 +15162,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -15243,7 +15171,7 @@
         <v>88</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>100</v>
@@ -15252,7 +15180,7 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
@@ -15263,10 +15191,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15289,13 +15217,13 @@
         <v>78</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15346,7 +15274,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -15364,7 +15292,7 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
@@ -15375,14 +15303,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -15401,16 +15329,16 @@
         <v>78</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N122" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -15448,19 +15376,19 @@
         <v>78</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -15472,13 +15400,13 @@
         <v>78</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>78</v>
@@ -15489,14 +15417,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -15515,19 +15443,19 @@
         <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N123" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L123" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O123" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -15576,7 +15504,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -15588,7 +15516,7 @@
         <v>78</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>78</v>
@@ -15605,10 +15533,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15634,13 +15562,13 @@
         <v>108</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15666,13 +15594,13 @@
         <v>78</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>78</v>
@@ -15690,7 +15618,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -15719,10 +15647,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15745,16 +15673,16 @@
         <v>89</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -15804,7 +15732,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -15833,10 +15761,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15859,13 +15787,13 @@
         <v>89</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -15916,7 +15844,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -15925,7 +15853,7 @@
         <v>88</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>100</v>
@@ -15934,7 +15862,7 @@
         <v>78</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>78</v>
@@ -15945,10 +15873,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15971,13 +15899,13 @@
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16028,7 +15956,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -16046,7 +15974,7 @@
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
@@ -16057,14 +15985,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16083,16 +16011,16 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N128" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -16130,19 +16058,19 @@
         <v>78</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16154,13 +16082,13 @@
         <v>78</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>78</v>
@@ -16171,14 +16099,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -16197,19 +16125,19 @@
         <v>89</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L129" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O129" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -16258,7 +16186,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -16270,7 +16198,7 @@
         <v>78</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>78</v>
@@ -16287,10 +16215,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16316,10 +16244,10 @@
         <v>108</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -16346,13 +16274,13 @@
         <v>78</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>78</v>
@@ -16370,7 +16298,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>88</v>
@@ -16399,10 +16327,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16428,13 +16356,13 @@
         <v>102</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -16484,7 +16412,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>88</v>
@@ -16513,10 +16441,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16539,17 +16467,15 @@
         <v>89</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -16598,7 +16524,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -16627,10 +16553,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16653,17 +16579,15 @@
         <v>89</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -16712,7 +16636,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -16741,10 +16665,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16767,17 +16691,15 @@
         <v>89</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -16826,7 +16748,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -16855,10 +16777,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16881,17 +16803,15 @@
         <v>89</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -16940,7 +16860,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -16969,10 +16889,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16995,13 +16915,13 @@
         <v>89</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -17052,7 +16972,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -17061,7 +16981,7 @@
         <v>88</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>100</v>
@@ -17070,7 +16990,7 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>78</v>
@@ -17081,10 +17001,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17107,13 +17027,13 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -17164,7 +17084,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -17182,7 +17102,7 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>78</v>
@@ -17193,14 +17113,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -17219,16 +17139,16 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N138" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -17266,19 +17186,19 @@
         <v>78</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -17290,13 +17210,13 @@
         <v>78</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>78</v>
@@ -17307,14 +17227,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -17333,19 +17253,19 @@
         <v>89</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N139" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L139" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="O139" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>78</v>
@@ -17394,7 +17314,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -17406,7 +17326,7 @@
         <v>78</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>78</v>
@@ -17423,10 +17343,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17449,17 +17369,15 @@
         <v>89</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -17508,7 +17426,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>88</v>
@@ -17537,10 +17455,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17566,14 +17484,12 @@
         <v>102</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -17622,7 +17538,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -17651,10 +17567,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17677,16 +17593,16 @@
         <v>89</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -17736,7 +17652,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -17765,10 +17681,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17791,16 +17707,16 @@
         <v>89</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -17850,7 +17766,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -17879,10 +17795,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17905,16 +17821,16 @@
         <v>89</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -17964,7 +17880,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -17982,7 +17898,7 @@
         <v>78</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>78</v>
@@ -17993,10 +17909,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18019,19 +17935,19 @@
         <v>89</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -18080,7 +17996,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -18089,7 +18005,7 @@
         <v>88</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>100</v>
@@ -18098,7 +18014,7 @@
         <v>78</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>78</v>
